--- a/dados/excel/municipio_escolaridade.xlsx
+++ b/dados/excel/municipio_escolaridade.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>4286.16</v>
+        <v>4281.15</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>3745.37</v>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>5781.82</v>
+        <v>5812.83</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>5316.73</v>
+        <v>5316.72</v>
       </c>
     </row>
     <row r="4">
@@ -849,10 +849,10 @@
         <v>280</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>5371.49</v>
+        <v>5285.38</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>4614.73</v>
+        <v>4515.15</v>
       </c>
     </row>
     <row r="5">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>6769.56</v>
+        <v>7479.74</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>5543.02</v>
+        <v>6874.66</v>
       </c>
     </row>
     <row r="6">
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>3592</v>
+        <v>3625</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>5858.13</v>
+        <v>5872.18</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>5194.78</v>
+        <v>5167.26</v>
       </c>
     </row>
     <row r="7">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>934</v>
+        <v>993</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>2182.01</v>
+        <v>2373.36</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>1084.8</v>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>6887</v>
+        <v>7306</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>8604.52</v>
+        <v>8583.290000000001</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>7478.65</v>
+        <v>7150.18</v>
       </c>
     </row>
     <row r="9">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>1898</v>
+        <v>1934</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>15811.58</v>
+        <v>15551.29</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>14133.37</v>
+        <v>14035.95</v>
       </c>
     </row>
     <row r="10">
@@ -972,13 +972,13 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>21657.42</v>
+        <v>20470.98</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>17931.19</v>
+        <v>17589.04</v>
       </c>
     </row>
     <row r="11">
@@ -996,7 +996,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>22573.96</v>
+        <v>22600.99</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>21133.89</v>
